--- a/results/02_taxa_assemblage/LDA_Method/ModelC_Weighted/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelC_Weighted/tables/site_eval_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3461131217975691</v>
+        <v>0.3502596381018384</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3411344859462137</v>
+        <v>0.6475096809600893</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3127523922562172</v>
+        <v>0.002230680938072302</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3461131217975691</v>
+        <v>0.6475096809600893</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004978635851355384</v>
+        <v>0.297250042858251</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1245581292228475</v>
+        <v>0.4903479704870848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3152272943660737</v>
+        <v>0.1343279499890021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5602145764110789</v>
+        <v>0.3753240795239131</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5602145764110789</v>
+        <v>0.4903479704870848</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2449872820450052</v>
+        <v>0.1150238909631717</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -563,30 +563,30 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.08219243510319008</v>
+        <v>0.3786366694497317</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5000177263074058</v>
+        <v>0.1236260770722447</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4177898385894041</v>
+        <v>0.4977372534780236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5000177263074058</v>
+        <v>0.4977372534780236</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08222788771800171</v>
+        <v>0.1191005840282919</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3957738059934418</v>
+        <v>0.8790298553165987</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1405988383713781</v>
+        <v>0.07889365201618943</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4636273556351802</v>
+        <v>0.04207649266721188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4636273556351802</v>
+        <v>0.8790298553165987</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06785354964173845</v>
+        <v>0.8001362033004092</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -643,26 +643,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02070426169545483</v>
+        <v>0.08652911050782569</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7929277034533205</v>
+        <v>0.9057256382473435</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1863680348512246</v>
+        <v>0.007745251244830807</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7929277034533205</v>
+        <v>0.9057256382473435</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6065596686020959</v>
+        <v>0.8191965277395179</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01165883092253963</v>
+        <v>0.02467779496703325</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9186095562043429</v>
+        <v>0.9744792287968538</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06973161287311727</v>
+        <v>0.0008429762361130397</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9186095562043429</v>
+        <v>0.9744792287968538</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8488779433312257</v>
+        <v>0.9498014338298205</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -726,19 +726,19 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05349257035612547</v>
+        <v>0.3078121395446793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7405307896080455</v>
+        <v>0.6708804477227081</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2059766400358289</v>
+        <v>0.02130741273261252</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7405307896080455</v>
+        <v>0.6708804477227081</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5345541495722166</v>
+        <v>0.3630683081780287</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -764,19 +764,19 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00178537413651823</v>
+        <v>0.003013521193970868</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8523685906342122</v>
+        <v>0.9969185256706682</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1458460352292694</v>
+        <v>6.7953135361045e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8523685906342122</v>
+        <v>0.9969185256706682</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7065225554049428</v>
+        <v>0.9939050044766973</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -802,19 +802,19 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05194090420455254</v>
+        <v>0.4627893710024393</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7049823429139433</v>
+        <v>0.4946078873027226</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2430767528815042</v>
+        <v>0.04260274169483805</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7049823429139433</v>
+        <v>0.4946078873027226</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4619055900324391</v>
+        <v>0.03181851630028332</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -840,19 +840,19 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1333375632703744</v>
+        <v>0.3055008464299688</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6925247388939348</v>
+        <v>0.6869472761283262</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1741376978356907</v>
+        <v>0.007551877441704847</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6925247388939348</v>
+        <v>0.6869472761283262</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5183870410582442</v>
+        <v>0.3814464296983573</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04165671772885381</v>
+        <v>0.02914026365847436</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8462393623096954</v>
+        <v>0.9705140662865719</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1121039199614508</v>
+        <v>0.0003456700549537333</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8462393623096954</v>
+        <v>0.9705140662865719</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7341354423482446</v>
+        <v>0.9413738026280976</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -905,30 +905,30 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06175869784691664</v>
+        <v>0.9772351771847076</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001002284488103893</v>
+        <v>0.0002240290236751304</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9372390176649795</v>
+        <v>0.02254079379161722</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9372390176649795</v>
+        <v>0.9772351771847076</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8754803198180628</v>
+        <v>0.9546943833930904</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -943,30 +943,30 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1471340306314695</v>
+        <v>0.6626876695044266</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02425924050628182</v>
+        <v>0.00357099200511642</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8286067288622486</v>
+        <v>0.3337413384904571</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8286067288622486</v>
+        <v>0.6626876695044266</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6814726982307792</v>
+        <v>0.3289463310139695</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07847281995358925</v>
+        <v>0.50730900351939</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4612766083508454</v>
+        <v>0.2476817100878175</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4602505716955653</v>
+        <v>0.2450092863927925</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4612766083508454</v>
+        <v>0.50730900351939</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001026036655280116</v>
+        <v>0.2596272934315725</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001213621800949219</v>
+        <v>0.002680336133506194</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9635749518018136</v>
+        <v>0.9920102656318691</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03521142639723722</v>
+        <v>0.005309398234624623</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9635749518018136</v>
+        <v>0.9920102656318691</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9283635254045765</v>
+        <v>0.9867008673972445</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1061,26 +1061,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01312989969407601</v>
+        <v>0.04830353378236373</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8611519481982328</v>
+        <v>0.9020057282686194</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1257181521076912</v>
+        <v>0.04969073794901697</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8611519481982328</v>
+        <v>0.9020057282686194</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7354337960905416</v>
+        <v>0.8523149903196023</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1106,19 +1106,19 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.123401838696589</v>
+        <v>0.05434025125503906</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6283157077555966</v>
+        <v>0.9451375402027543</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2482824535478144</v>
+        <v>0.0005222085422066682</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6283157077555966</v>
+        <v>0.9451375402027543</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3800332542077822</v>
+        <v>0.8907972889477153</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1141,22 +1141,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3031689073323018</v>
+        <v>0.8121585901306853</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2250380234031703</v>
+        <v>0.1332255987129218</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4717930692645279</v>
+        <v>0.05461581115639299</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4717930692645279</v>
+        <v>0.8121585901306853</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1686241619322261</v>
+        <v>0.6789329914177635</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1182,19 +1182,19 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4399330219886847</v>
+        <v>0.9449526536839092</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2027205258714516</v>
+        <v>0.05406853478450631</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3573464521398638</v>
+        <v>0.0009788115315844997</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4399330219886847</v>
+        <v>0.9449526536839092</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0825865698488209</v>
+        <v>0.8908841188994029</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1205,34 +1205,34 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07874485839137123</v>
+        <v>0.6514304286551785</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7502873341735541</v>
+        <v>0.3406278158127664</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1709678074350746</v>
+        <v>0.007941755532055053</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7502873341735541</v>
+        <v>0.6514304286551785</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5793195267384795</v>
+        <v>0.3108026128424122</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1243,11 +1243,11 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2762905059910711</v>
+        <v>0.1325749167032254</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09838023227852559</v>
+        <v>0.8642255196534242</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6253292617304034</v>
+        <v>0.003199563643350513</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6253292617304034</v>
+        <v>0.8642255196534242</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3490387557393323</v>
+        <v>0.7316506029501988</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1289,26 +1289,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1356497242874611</v>
+        <v>0.5188533616980245</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1325528172242225</v>
+        <v>0.1676814919116666</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7317974584883166</v>
+        <v>0.3134651463903089</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7317974584883166</v>
+        <v>0.5188533616980245</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5961477342008554</v>
+        <v>0.2053882153077156</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1334,19 +1334,19 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.446605255920533</v>
+        <v>0.8276529900154419</v>
       </c>
       <c r="F24" t="n">
-        <v>0.113801301417531</v>
+        <v>0.04489059748301943</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4395934426619359</v>
+        <v>0.1274564125015387</v>
       </c>
       <c r="H24" t="n">
-        <v>0.446605255920533</v>
+        <v>0.8276529900154419</v>
       </c>
       <c r="I24" t="n">
-        <v>0.007011813258597066</v>
+        <v>0.7001965775139032</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1369,22 +1369,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1459996891117744</v>
+        <v>0.3153933996276246</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4646466963438954</v>
+        <v>0.2622782824278182</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3893536145443302</v>
+        <v>0.4223283179445573</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4646466963438954</v>
+        <v>0.4223283179445573</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07529308179956518</v>
+        <v>0.1069349183169327</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1407,22 +1407,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.377532286058239</v>
+        <v>0.8706200857721241</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1652411564535467</v>
+        <v>0.04590281816676887</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4572265574882141</v>
+        <v>0.083477096061107</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4572265574882141</v>
+        <v>0.8706200857721241</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07969427142997509</v>
+        <v>0.7871429897110171</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4105042619910664</v>
+        <v>0.7221902053923605</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05046533420854049</v>
+        <v>0.118309632154694</v>
       </c>
       <c r="G27" t="n">
-        <v>0.539030403800393</v>
+        <v>0.1595001624529457</v>
       </c>
       <c r="H27" t="n">
-        <v>0.539030403800393</v>
+        <v>0.7221902053923605</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1285261418093266</v>
+        <v>0.5626900429394148</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1483,22 +1483,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5300402797369621</v>
+        <v>0.4773936529822903</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1057820854391848</v>
+        <v>0.4969302930783435</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3641776348238533</v>
+        <v>0.02567605393936616</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5300402797369621</v>
+        <v>0.4969302930783435</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1658626449131088</v>
+        <v>0.01953664009605316</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1524,19 +1524,19 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7166151174749492</v>
+        <v>0.7886180585602056</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01619944467661952</v>
+        <v>0.1135930293662509</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2671854378484312</v>
+        <v>0.09778891207354345</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7166151174749492</v>
+        <v>0.7886180585602056</v>
       </c>
       <c r="I29" t="n">
-        <v>0.449429679626518</v>
+        <v>0.6750250291939547</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1547,11 +1547,11 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3703321789751203</v>
+        <v>0.9427052233497784</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0452095136857576</v>
+        <v>0.01441908332064754</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5844583073391221</v>
+        <v>0.04287569332957415</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5844583073391221</v>
+        <v>0.9427052233497784</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2141261283640017</v>
+        <v>0.8998295300202042</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1585,11 +1585,11 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3733159478278834</v>
+        <v>0.9183290056543428</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07492686133382623</v>
+        <v>0.04742769141086348</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5517571908382903</v>
+        <v>0.03424330293479369</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5517571908382903</v>
+        <v>0.9183290056543428</v>
       </c>
       <c r="I31" t="n">
-        <v>0.178441243010407</v>
+        <v>0.8709013142434794</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1623,34 +1623,34 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3955076124256895</v>
+        <v>0.9879480997103753</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09811136377522059</v>
+        <v>0.0103863553464196</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5063810237990899</v>
+        <v>0.001665544943205181</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5063810237990899</v>
+        <v>0.9879480997103753</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1108734113734004</v>
+        <v>0.9775617443639557</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1669,26 +1669,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.451243590771796</v>
+        <v>0.7703662439322601</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1359924656214723</v>
+        <v>0.003964992277057059</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4127639436067319</v>
+        <v>0.2256687637906829</v>
       </c>
       <c r="H33" t="n">
-        <v>0.451243590771796</v>
+        <v>0.7703662439322601</v>
       </c>
       <c r="I33" t="n">
-        <v>0.03847964716506413</v>
+        <v>0.5446974801415772</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1699,11 +1699,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.339123687268267</v>
+        <v>0.7662273873953076</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1782089263187831</v>
+        <v>0.0137257571531525</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4826673864129499</v>
+        <v>0.2200468554515399</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4826673864129499</v>
+        <v>0.7662273873953076</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1435436991446828</v>
+        <v>0.5461805319437677</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1737,11 +1737,11 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2683062694458951</v>
+        <v>0.7954505601215629</v>
       </c>
       <c r="F35" t="n">
-        <v>0.08776629855242032</v>
+        <v>0.02644787698354218</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6439274320016846</v>
+        <v>0.178101562894895</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6439274320016846</v>
+        <v>0.7954505601215629</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3756211625557895</v>
+        <v>0.6173489972266679</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1783,26 +1783,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4641779651135518</v>
+        <v>0.7589387145775602</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1252758796454663</v>
+        <v>0.04114456248074353</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4105461552409818</v>
+        <v>0.1999167229416962</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4641779651135518</v>
+        <v>0.7589387145775602</v>
       </c>
       <c r="I36" t="n">
-        <v>0.05363180987256999</v>
+        <v>0.5590219916358641</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1813,11 +1813,11 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1623065926656882</v>
+        <v>0.6656602142578654</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4642164675541985</v>
+        <v>0.03546695273457421</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3734769397801132</v>
+        <v>0.2988728330075603</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4642164675541985</v>
+        <v>0.6656602142578654</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09073952777408528</v>
+        <v>0.366787381250305</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1859,26 +1859,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2781903427332619</v>
+        <v>0.8068261561066493</v>
       </c>
       <c r="F38" t="n">
-        <v>0.215058930485102</v>
+        <v>0.02269570388844116</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5067507267816361</v>
+        <v>0.1704781400049095</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5067507267816361</v>
+        <v>0.8068261561066493</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2285603840483743</v>
+        <v>0.6363480161017399</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1889,34 +1889,34 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1654944819909287</v>
+        <v>0.7862630099136995</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4719890152687199</v>
+        <v>0.04137403927121999</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3625165027403514</v>
+        <v>0.1723629508150807</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4719890152687199</v>
+        <v>0.7862630099136995</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1094725125283685</v>
+        <v>0.6139000590986188</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1927,34 +1927,34 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4173694956437476</v>
+        <v>0.4772955728455939</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1466963346728159</v>
+        <v>0.1714602526394167</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4359341696834364</v>
+        <v>0.3512441745149893</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4359341696834364</v>
+        <v>0.4772955728455939</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01856467403968876</v>
+        <v>0.1260513983306045</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1980,19 +1980,19 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2360367837050362</v>
+        <v>0.3249897662901636</v>
       </c>
       <c r="F41" t="n">
-        <v>0.08253654029648641</v>
+        <v>0.0194674246966537</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6814266759984774</v>
+        <v>0.6555428090131827</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6814266759984774</v>
+        <v>0.6555428090131827</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4453898922934412</v>
+        <v>0.3305530427230191</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2003,11 +2003,11 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2015,22 +2015,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1074907321093684</v>
+        <v>0.7637674789133623</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5802543519394856</v>
+        <v>0.04378176357380116</v>
       </c>
       <c r="G42" t="n">
-        <v>0.312254915951146</v>
+        <v>0.1924507575128366</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5802543519394856</v>
+        <v>0.7637674789133623</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2679994359883396</v>
+        <v>0.5713167214005257</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2041,34 +2041,34 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S69</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1071376172349782</v>
+        <v>0.3498194435684507</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4438109024146363</v>
+        <v>0.004657567843288662</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4490514803503857</v>
+        <v>0.6455229885882606</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4490514803503857</v>
+        <v>0.6455229885882606</v>
       </c>
       <c r="I43" t="n">
-        <v>0.005240577935749391</v>
+        <v>0.2957035450198099</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2087,26 +2087,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2151727809077797</v>
+        <v>0.3407361078746282</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3505568875726376</v>
+        <v>0.3171519573328041</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4342703315195827</v>
+        <v>0.3421119347925678</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4342703315195827</v>
+        <v>0.3421119347925678</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08371344394694508</v>
+        <v>0.001375826917939638</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2117,34 +2117,34 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3589319270284989</v>
+        <v>0.2384314015352692</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1817082705942868</v>
+        <v>0.1190047997667654</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4593598023772143</v>
+        <v>0.6425637986979653</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4593598023772143</v>
+        <v>0.6425637986979653</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1004278753487154</v>
+        <v>0.4041323971626961</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>S74</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2163,28 +2163,142 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6345544546964776</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1028088142922197</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.2626367310113025</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6345544546964776</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.3719177236851751</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>S79</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.6542981496977957</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.2727036748673941</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.07299817543481031</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6542981496977957</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.3815944748304016</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.7784650856539509</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.05858905482021308</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1629458595258359</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7784650856539509</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6155192261281149</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>S81</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>2</v>
       </c>
-      <c r="E46" t="n">
-        <v>0.08161060950482354</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.5132665866858468</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.4051228038093297</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.5132665866858468</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.1081437828765171</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="E49" t="n">
+        <v>0.05638125143626642</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9416485917240753</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.001970156839658314</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9416485917240753</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.885267340287809</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
